--- a/Livrables/00-Base-Commune/01-SWOT.xlsx
+++ b/Livrables/00-Base-Commune/01-SWOT.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,24 +26,47 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="DejaVu Sans"/>
       <b val="1"/>
-      <color rgb="001B3A5B"/>
-      <sz val="20"/>
+      <color rgb="00C89B3F"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="DejaVu Sans"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="000A2342"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="DejaVu Sans"/>
+      <i val="1"/>
+      <color rgb="004B5563"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <color rgb="00222222"/>
+      <name val="DejaVu Sans"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="DejaVu Sans"/>
+      <i val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="DejaVu Sans"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="DejaVu Sans"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -52,42 +75,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E7D32"/>
+        <fgColor rgb="00047857"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F5E9"/>
+        <fgColor rgb="00B91C1C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C62828"/>
+        <fgColor rgb="001D4ED8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEBEE"/>
+        <fgColor rgb="00C2410C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001565C0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E3F2FD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EF6C00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3E0"/>
+        <fgColor rgb="00F5F7FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -101,49 +109,58 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="00E5E7EB"/>
       </left>
       <right style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="00E5E7EB"/>
       </right>
       <top style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="00E5E7EB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="00E5E7EB"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -509,269 +526,296 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A2:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SWOT - Groupe Torpier</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="26" customHeight="1">
+    <row r="1" ht="6" customHeight="1"/>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>PHASE 1 - ANALYSE DE L'EXISTANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Forces (Strengths)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Faiblesses (Weaknesses)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Opportunites (Opportunities)</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Menaces (Threats)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>- Notoriete et heritage (entreprise familiale depuis 1862)</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>- Pas de PRA / PCA formalise (incendie -&gt; 150 K EUR de perte)</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>- Expansion europeenne : Allemagne, Italie, Espagne, Finlande</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>- Cybermenaces croissantes (ransomware, phishing) amplifiees par le teletravail</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>- Croissance soutenue : +30 % de CA entre 2023 et 2025</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>- Echanges CSV fragiles entre GesProd et Dynamics</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>- Marche B2B prive (promoteurs immobiliers) en croissance</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>- Pression reglementaire : RGPD, NIS 2, CSRD</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>- Expertise bois + design ecoresponsable (Sophie Crelin, Samir Oufrani)</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>- Workflow de commandes via mail + Excel (atelier fabrication)</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>- Demande clients pour des produits ecoresponsables et traces</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>- Obsolescence technologique (Windows 2019, Exchange on-prem, VPN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>- Virage e-commerce reussi (PrestaShop + bots SAV)</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>- Pas de replique AD DS en Finlande</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>- Industrie 4.0 : IoT, maintenance predictive, automatisation</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>- Dependance a des applications internes vieillissantes (GesProd, DocuFlow)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>- DSI structuree : DSI, Infra/Securite, PMO, Applicatif + devs</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>- VLAN unique Production + Conception (cloisonnement insuffisant)</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>- Maturite du cloud (M365, Azure, iPaaS)</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>- Penurie de competences IT et industrielles sur le marche</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>- Tiffany Valentia (PMP + Scrum Master) porte la cellule PMO</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>- Migration Exchange non finalisee</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>- Cadres reglementaires (RGPD, CSRD) valorisant la conformite</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>- Volatilite des cours du bois et tensions d'approvisionnement</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>- Socle technique solide : cluster SQL AlwaysOn, Veeam, AD DS, GitLab</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>- Processus ITIL immatures (problemes, changement, connaissance)</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>- Ecosystemes d'API et de donnees ouvertes (integration facilitee)</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>- Concurrence europeenne accrue (entree sur de nouveaux marches)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>- Jira Service Management deploye (base ITIL)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>- Absence de MFA / SSO central face au teletravail croissant</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>- Disponibilite de freelances pour absorber les pics de charge</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>- Risque d'incident physique (incendie, sinistre site)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>- Culture SI presente chez les utilisateurs</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>- VPN IPSec vieillissant pour 5+ sites europeens</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>- Direction fortement impliquee dans la strategie SI</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>- Serveurs Windows Server 2019 en fin de vie</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>- Processus de pilotage des projets SI en construction</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>- Aucun tableau de bord d'usage / service IT pour les metiers</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>- Barriere linguistique et culturelle avec l'usine finlandaise</t>
+          <t>SWOT du Groupe Torpier</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Diagnostic strategique - synthese interne et environnement externe</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>FORCES</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>FAIBLESSES</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>OPPORTUNITES</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>MENACES</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Atouts internes a capitaliser</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Points faibles a corriger</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Leviers externes a saisir</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Risques externes a anticiper</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>-  Entreprise familiale depuis 1862, notoriete etablie</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>-  Aucun PRA / PCA formalise (incendie = 150 K EUR)</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>-  Expansion europeenne : DE, IT, ES, Finlande</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>-  Cybermenaces amplifiees par le teletravail</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>-  Croissance forte : +30 % de CA sur 2023-2025</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>-  Echanges CSV fragiles GesProd - Dynamics</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>-  Nouveau segment B2B prive (promoteurs immobiliers)</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>-  Obsolescence technologique (Exchange, Win 2019, VPN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>-  Virage e-commerce reussi (PrestaShop + bots SAV)</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>-  Commandes production via mail + Excel</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>-  Demande clients produits ecoresponsables et traces</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>-  Pression reglementaire RGPD, NIS 2, CSRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>-  DSI structuree (DSI, Infra, PMO, Applicatif + devs)</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>-  Pas de replica AD DS sur l'usine finlandaise</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>-  Industrie 4.0 : IoT, maintenance predictive</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>-  Dependance a des applis internes vieillissantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>-  Tiffany Valentia PMP + Scrum Master en cellule PMO</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>-  VLAN unique Production + Conception (cloisonnement)</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>-  Maturite cloud (Microsoft 365, Azure, iPaaS)</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>-  Penurie de competences IT et industrielles</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>-  Socle technique solide : SQL AlwaysOn, Veeam, AD DS</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>-  Migration Exchange non finalisee</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>-  Cadres reglementaires RGPD, NIS 2, CSRD</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>-  Volatilite des cours du bois et approvisionnement</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>-  Jira Service Management deploye (amorce ITIL)</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>-  Processus ITIL immatures (problemes, changements)</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>-  Ecosysteme d'API ouvert pour integrer les applis</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>-  Concurrence europeenne accrue</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>-  Direction impliquee dans la strategie SI</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>-  Absence de MFA / SSO face au teletravail croissant</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>-  Freelances mobilisables pour absorber la charge</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>-  Risques d'incident physique (incendie, sinistre)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>-  Culture SI presente chez les utilisateurs</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>-  Serveurs Windows 2019 proches de l'obsolescence</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr"/>
+      <c r="D16" s="12" t="inlineStr"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="13" t="inlineStr"/>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>-  Processus de pilotage des projets SI en construction</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr"/>
+      <c r="D17" s="13" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Groupe Torpier | SDSI 2026-2029  |  DSI Torpier  |  v1.0</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="4">
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>